--- a/data/stx_xlsx/PIONb.ST.xlsx
+++ b/data/stx_xlsx/PIONb.ST.xlsx
@@ -9570,14 +9570,38 @@
       <c r="O47" s="18">
         <v>4.35</v>
       </c>
-      <c r="P47" s="19"/>
-      <c r="Q47" s="19"/>
-      <c r="R47" s="19"/>
-      <c r="S47" s="19"/>
-      <c r="T47" s="19"/>
-      <c r="U47" s="19"/>
-      <c r="V47" s="19"/>
-      <c r="W47" s="19"/>
+      <c r="P47" s="18">
+        <f t="shared" ref="P47:W47" si="1">SUM(P49,P51)</f>
+        <v>2.81</v>
+      </c>
+      <c r="Q47" s="18">
+        <f t="shared" si="1"/>
+        <v>2.83</v>
+      </c>
+      <c r="R47" s="18">
+        <f t="shared" si="1"/>
+        <v>4.03</v>
+      </c>
+      <c r="S47" s="18">
+        <f t="shared" si="1"/>
+        <v>6.33</v>
+      </c>
+      <c r="T47" s="18">
+        <f t="shared" si="1"/>
+        <v>6.87</v>
+      </c>
+      <c r="U47" s="18">
+        <f t="shared" si="1"/>
+        <v>5.36</v>
+      </c>
+      <c r="V47" s="18">
+        <f t="shared" si="1"/>
+        <v>3.65</v>
+      </c>
+      <c r="W47" s="18">
+        <f t="shared" si="1"/>
+        <v>5.96</v>
+      </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
